--- a/data/trans_bre/P1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,3</t>
+          <t>-0,95; 3,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,9</t>
+          <t>0,35; 4,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,98</t>
+          <t>-1,99; 2,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,96</t>
+          <t>1,38; 10,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 358,28</t>
+          <t>-44,92; 356,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 427,53</t>
+          <t>2,47; 419,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 162,39</t>
+          <t>-62,66; 169,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; —</t>
+          <t>-50,52; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,75</t>
+          <t>1,2; 5,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,67</t>
+          <t>0,12; 4,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,34</t>
+          <t>-2,21; 2,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,88</t>
+          <t>-1,44; 5,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 310,95</t>
+          <t>25,36; 318,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 250,63</t>
+          <t>0,3; 252,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 94,64</t>
+          <t>-44,56; 103,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 398,89</t>
+          <t>-36,34; 356,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,4</t>
+          <t>-1,3; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 9,67</t>
+          <t>3,77; 9,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,14</t>
+          <t>0,17; 4,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,37</t>
+          <t>-2,78; 2,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 123,57</t>
+          <t>-26,07; 116,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,11; 301,9</t>
+          <t>54,27; 296,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 215,41</t>
+          <t>3,23; 218,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 63,7</t>
+          <t>-39,71; 63,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,51</t>
+          <t>1,98; 8,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,8</t>
+          <t>2,99; 9,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,23</t>
+          <t>0,41; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,47</t>
+          <t>0,88; 8,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,69; 252,2</t>
+          <t>31,02; 261,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,62; 196,84</t>
+          <t>34,5; 198,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 124,26</t>
+          <t>4,76; 123,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 366,37</t>
+          <t>11,15; 374,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 6,31</t>
+          <t>-1,72; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 14,97</t>
+          <t>5,91; 15,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,63</t>
+          <t>6,22; 14,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,94</t>
+          <t>1,9; 7,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 110,55</t>
+          <t>-20,16; 109,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,29; 212,03</t>
+          <t>51,66; 204,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,87; 341,08</t>
+          <t>75,0; 364,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,64; 133,81</t>
+          <t>20,65; 123,19</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 8,75</t>
+          <t>-1,4; 8,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,4</t>
+          <t>2,32; 14,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,97; 14,05</t>
+          <t>4,1; 14,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 7,37</t>
+          <t>-5,37; 7,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 106,45</t>
+          <t>-12,02; 107,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,25; 152,05</t>
+          <t>13,82; 150,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,63; 207,47</t>
+          <t>34,1; 226,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,1; 106,35</t>
+          <t>-55,51; 108,3</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 9,11</t>
+          <t>-3,86; 9,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 17,73</t>
+          <t>2,99; 17,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,46</t>
+          <t>6,94; 19,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,12</t>
+          <t>9,94; 17,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 73,37</t>
+          <t>-20,36; 73,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,46; 106,03</t>
+          <t>11,36; 102,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,97; 211,96</t>
+          <t>47,36; 219,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72,43; 214,86</t>
+          <t>74,42; 211,71</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,54</t>
+          <t>2,05; 4,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,68</t>
+          <t>5,79; 8,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,57</t>
+          <t>4,07; 6,64</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,18</t>
+          <t>2,68; 6,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,16; 97,34</t>
+          <t>35,16; 96,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,5; 140,91</t>
+          <t>79,72; 146,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,92; 137,83</t>
+          <t>69,26; 140,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,94; 135,45</t>
+          <t>45,71; 133,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1002-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>589,02%</t>
+          <t>408,09%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,11</t>
+          <t>-0,94; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,91</t>
+          <t>0,43; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,16</t>
+          <t>-1,78; 2,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,02</t>
+          <t>1,04; 9,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 356,76</t>
+          <t>-37,09; 330,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 419,84</t>
+          <t>3,39; 405,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-62,66; 169,4</t>
+          <t>-57,42; 201,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,52; —</t>
+          <t>-38,86; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,9</t>
+          <t>1,35; 5,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 4,48</t>
+          <t>0,28; 4,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,52</t>
+          <t>-2,12; 2,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 5,74</t>
+          <t>-0,48; 6,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,36; 318,71</t>
+          <t>29,98; 342,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 252,63</t>
+          <t>4,02; 263,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 103,02</t>
+          <t>-42,55; 97,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,34; 356,12</t>
+          <t>-18,66; 409,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,45</t>
+          <t>-1,41; 3,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,86</t>
+          <t>3,49; 9,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,95</t>
+          <t>0,45; 5,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,49</t>
+          <t>-2,09; 2,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 116,12</t>
+          <t>-28,17; 114,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,27; 296,86</t>
+          <t>54,06; 297,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 218,02</t>
+          <t>5,01; 229,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 63,28</t>
+          <t>-31,93; 80,57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>2,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,49</t>
+          <t>1,81; 8,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,97</t>
+          <t>2,85; 10,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,14</t>
+          <t>0,26; 6,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,66</t>
+          <t>-0,75; 4,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,02; 261,7</t>
+          <t>28,77; 239,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,5; 198,14</t>
+          <t>33,81; 196,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 123,48</t>
+          <t>1,92; 135,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 374,11</t>
+          <t>-9,54; 97,37</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,73</t>
+          <t>5,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 6,15</t>
+          <t>-1,94; 6,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 15,12</t>
+          <t>5,63; 15,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 14,45</t>
+          <t>6,36; 14,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,5</t>
+          <t>2,41; 8,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 109,79</t>
+          <t>-20,61; 109,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,66; 204,6</t>
+          <t>49,16; 222,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,0; 364,47</t>
+          <t>72,62; 335,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,65; 123,19</t>
+          <t>24,93; 144,05</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 8,81</t>
+          <t>-1,32; 8,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 14,52</t>
+          <t>2,31; 14,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,54</t>
+          <t>3,37; 14,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 7,43</t>
+          <t>3,66; 10,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 107,82</t>
+          <t>-9,24; 101,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,82; 150,19</t>
+          <t>12,17; 146,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,1; 226,74</t>
+          <t>31,3; 225,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,51; 108,3</t>
+          <t>34,48; 173,77</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,85</t>
+          <t>13,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>128,25%</t>
+          <t>122,39%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 9,06</t>
+          <t>-4,16; 8,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,78</t>
+          <t>2,9; 17,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 19,3</t>
+          <t>6,25; 18,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,66</t>
+          <t>9,11; 17,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 73,36</t>
+          <t>-21,32; 68,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,36; 102,89</t>
+          <t>11,26; 102,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,36; 219,52</t>
+          <t>40,1; 205,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74,42; 211,71</t>
+          <t>63,6; 187,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,55</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,54</t>
+          <t>2,06; 4,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,85</t>
+          <t>5,72; 8,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,07; 6,64</t>
+          <t>3,99; 6,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,18</t>
+          <t>3,93; 6,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>35,16; 96,6</t>
+          <t>34,81; 97,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,72; 146,27</t>
+          <t>76,37; 141,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,26; 140,87</t>
+          <t>69,32; 141,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,71; 133,57</t>
+          <t>60,2; 119,47</t>
         </is>
       </c>
     </row>
